--- a/sigal/src/main/resources/plantillas/plantilla_importar_horario.xlsx
+++ b/sigal/src/main/resources/plantillas/plantilla_importar_horario.xlsx
@@ -1,51 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBD56A0-B3D2-4C71-9B25-399304EA4550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horario" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+  <si>
+    <t>Tipo de espacio</t>
+  </si>
+  <si>
+    <t>Nombre del espacio</t>
+  </si>
+  <si>
+    <t>Día</t>
+  </si>
+  <si>
+    <t>Hora de inicio</t>
+  </si>
+  <si>
+    <t>Hora de fin</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Laboratorio</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>8:50</t>
+  </si>
+  <si>
+    <t>9:00</t>
+  </si>
+  <si>
+    <t>9:50</t>
+  </si>
+  <si>
+    <t>Aula</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>GTID235</t>
+  </si>
+  <si>
+    <t>Aula TI -1</t>
+  </si>
+  <si>
+    <t>LAB TI - I</t>
+  </si>
+  <si>
+    <t>LAB TI - III</t>
+  </si>
+  <si>
+    <t>GTID232</t>
+  </si>
+  <si>
+    <t>Borre las filas de ejemplo antes de llenar el horario, a igual que este mensaje. Día: Lunes a Sábado. Horas en formato 8:00 (24 hrs).</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B6B66"/>
+      <i/>
       <sz val="9"/>
+      <color rgb="FF6B6B66"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00185FA5"/>
-        <bgColor rgb="00185FA5"/>
+        <fgColor rgb="FF185FA5"/>
+        <bgColor rgb="FF185FA5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,85 +140,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,155 +447,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de espacio</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre del espacio</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Día</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Hora de inicio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Hora de fin</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Laboratorio</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Laboratorio de Cómputo 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>8:50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Laboratorio</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Laboratorio de Cómputo 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>9:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>9:50</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Aula 204</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Borra las filas de ejemplo antes de llenar tu propio horario. Día: Lunes a Sábado. Horas en formato 8:00 (24 hrs).</t>
-        </is>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/sigal/src/main/resources/plantillas/plantilla_importar_horario.xlsx
+++ b/sigal/src/main/resources/plantillas/plantilla_importar_horario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBD56A0-B3D2-4C71-9B25-399304EA4550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3F7072-CD1C-404F-9613-0D3ABFDCA267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Tipo de espacio</t>
   </si>
@@ -86,13 +86,19 @@
   </si>
   <si>
     <t>Borre las filas de ejemplo antes de llenar el horario, a igual que este mensaje. Día: Lunes a Sábado. Horas en formato 8:00 (24 hrs).</t>
+  </si>
+  <si>
+    <t>Materia</t>
+  </si>
+  <si>
+    <t>(materia existente)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +117,14 @@
       <sz val="9"/>
       <color rgb="FF6B6B66"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,13 +153,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -456,9 +472,10 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,8 +494,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -497,8 +517,11 @@
       <c r="F2" t="s">
         <v>16</v>
       </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -517,8 +540,11 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -537,11 +563,18 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E12" s="5"/>
+      <c r="G12" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
